--- a/mappings/組合對照表.xlsx
+++ b/mappings/組合對照表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6564,54 +6564,54 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>29926095</t>
+          <t>29926085</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>101041150020</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.87</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>29926095</t>
+          <t>29926085</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>101041050007</t>
+          <t>101041150020</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液5ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>HHS005A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -6621,93 +6621,93 @@
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>29926096</t>
+          <t>29926095</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>107111430001</t>
+          <t>101041150020</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>輕透水感物理防曬液38ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>UMF038A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>29926100</t>
+          <t>29926095</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>20123029</t>
+          <t>101041050007</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕微導面膜8入組</t>
+          <t>玻尿酸保濕精華液5ML</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t>PB230701=HHM001X*8</t>
+          <t>HHS005A</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>29926101</t>
+          <t>29926096</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>115101040018</t>
+          <t>107111430001</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>積雪草舒敏精華面膜4入</t>
+          <t>輕透水感物理防曬液38ML</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>DMM004A</t>
+          <t>UMF038A</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
@@ -6717,39 +6717,39 @@
       </c>
       <c r="F197" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>29926101</t>
+          <t>29926100</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>115101040017</t>
+          <t>20123029</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>神經醯胺保濕精華面膜4入</t>
+          <t>玻尿酸保濕微導面膜8入組</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>DCM004A</t>
+          <t>PB230701=HHM001X*8</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6761,17 +6761,17 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>115101040019</t>
+          <t>115101040018</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>白藜蘆醇亮白精華面膜4入</t>
+          <t>積雪草舒敏精華面膜4入</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>DEM004A</t>
+          <t>DMM004A</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -6781,93 +6781,93 @@
       </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>29926102</t>
+          <t>29926101</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>115101040017</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽SHOT*7PCS</t>
+          <t>神經醯胺保濕精華面膜4入</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>DCM004A</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>29926102</t>
+          <t>29926101</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>115101040019</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
+          <t>白藜蘆醇亮白精華面膜4入</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>DEM004A</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>29926103</t>
+          <t>29926102</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽SHOT*7PCS</t>
+          <t>晚安雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
@@ -6884,7 +6884,7 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>29926103</t>
+          <t>29926102</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr">
@@ -6916,22 +6916,22 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>29926104</t>
+          <t>29926103</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
+          <t>水光雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>29926104</t>
+          <t>29926103</t>
         </is>
       </c>
       <c r="B205" s="1" t="inlineStr">
@@ -6980,54 +6980,54 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>29926105</t>
+          <t>29926104</t>
         </is>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽SHOT*7PCS</t>
+          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E206" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F206" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>29926105</t>
+          <t>29926104</t>
         </is>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
+          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E207" s="1" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F207" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -7049,17 +7049,17 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽SHOT*7PCS</t>
+          <t>水光雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -7069,29 +7069,29 @@
       </c>
       <c r="F208" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>29926107</t>
+          <t>29926105</t>
         </is>
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
@@ -7101,29 +7101,29 @@
       </c>
       <c r="F209" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>29926107</t>
+          <t>29926105</t>
         </is>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>122161050004</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油5ML</t>
+          <t>晚安雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t>QAS005A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E210" s="1" t="inlineStr">
@@ -7133,29 +7133,29 @@
       </c>
       <c r="F210" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>29926108</t>
+          <t>29926107</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>122161150001</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>角鯊潤澤修復精華油15ML</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>QAS015A</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
@@ -7172,22 +7172,22 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>29926108</t>
+          <t>29926107</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>122161050003</t>
+          <t>122161050004</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油5ML</t>
+          <t>角鯊潤澤修復精華油5ML</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>QRS005A</t>
+          <t>QAS005A</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
@@ -7204,118 +7204,118 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>29926106</t>
+          <t>29926108</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>102041170013</t>
+          <t>122161150004</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>AAS030A</t>
+          <t>QRS015A</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F213" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>29926110</t>
+          <t>29926108</t>
         </is>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>122161050003</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>角鯊玫瑰果賦活精華油5ML</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>QRS005A</t>
         </is>
       </c>
       <c r="E214" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F214" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>29926110</t>
+          <t>29926106</t>
         </is>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>151171070004</t>
+          <t>102041170013</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>SCP007A</t>
+          <t>AAS030A</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F215" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>29926111</t>
+          <t>29926110</t>
         </is>
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
@@ -7332,7 +7332,7 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>29926111</t>
+          <t>29926110</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr">
@@ -7364,22 +7364,22 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>29926112</t>
+          <t>29926111</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -7396,7 +7396,7 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>29926112</t>
+          <t>29926111</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr">
@@ -7428,54 +7428,54 @@
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>29926113</t>
+          <t>29926112</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>29926113</t>
+          <t>29926112</t>
         </is>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151171070004</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SCP007A</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
@@ -7497,17 +7497,17 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
@@ -7529,113 +7529,113 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>151171070004</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>SCP007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F223" s="1" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.27</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>29926114</t>
+          <t>29926113</t>
         </is>
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D224" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F224" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.27</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>29926114</t>
+          <t>29926113</t>
         </is>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>151171070004</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>SCP007A</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F225" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.18</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>29926115</t>
+          <t>29926114</t>
         </is>
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
@@ -7652,7 +7652,7 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>29926115</t>
+          <t>29926114</t>
         </is>
       </c>
       <c r="B227" s="1" t="inlineStr">
@@ -7684,22 +7684,22 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>29926116</t>
+          <t>29926115</t>
         </is>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E228" s="1" t="inlineStr">
@@ -7716,7 +7716,7 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>29926116</t>
+          <t>29926115</t>
         </is>
       </c>
       <c r="B229" s="1" t="inlineStr">
@@ -7748,86 +7748,86 @@
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>29926117</t>
+          <t>29926116</t>
         </is>
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E230" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F230" s="1" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>29926117</t>
+          <t>29926116</t>
         </is>
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E231" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F231" s="1" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>29926118</t>
+          <t>29926117</t>
         </is>
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D232" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E232" s="1" t="inlineStr">
@@ -7844,22 +7844,22 @@
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>29926118</t>
+          <t>29926117</t>
         </is>
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E233" s="1" t="inlineStr">
@@ -7876,22 +7876,22 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>29926119</t>
+          <t>29926118</t>
         </is>
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D234" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E234" s="1" t="inlineStr">
@@ -7908,22 +7908,22 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>29926119</t>
+          <t>29926118</t>
         </is>
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E235" s="1" t="inlineStr">
@@ -7940,86 +7940,86 @@
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>29926124</t>
+          <t>29926119</t>
         </is>
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8% 15ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D236" s="1" t="inlineStr">
         <is>
-          <t>RDS015A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E236" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F236" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>29926124</t>
+          <t>29926119</t>
         </is>
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>104041160001</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸淨痘調理精華20ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t>RSS020A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E237" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F237" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.17</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>29926126</t>
+          <t>29926124</t>
         </is>
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>104041150022</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>杏仁酸溫和煥膚精華8% 15ML</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>RDS015A</t>
         </is>
       </c>
       <c r="E238" s="1" t="inlineStr">
@@ -8029,29 +8029,29 @@
       </c>
       <c r="F238" s="1" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.52</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>29926126</t>
+          <t>29926124</t>
         </is>
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>107111180010</t>
+          <t>104041160001</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>全能保濕清爽防曬乳35ML</t>
+          <t>杏仁酸淨痘調理精華20ML</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>UHL035A</t>
+          <t>RSS020A</t>
         </is>
       </c>
       <c r="E239" s="1" t="inlineStr">
@@ -8061,29 +8061,29 @@
       </c>
       <c r="F239" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.48</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>29926127</t>
+          <t>29926126</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>101031250014</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華化妝水150ML</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t>HHT150A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E240" s="1" t="inlineStr">
@@ -8093,29 +8093,29 @@
       </c>
       <c r="F240" s="1" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.67</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>29926127</t>
+          <t>29926126</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>101041150020</t>
+          <t>107111180010</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>全能保濕清爽防曬乳35ML</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>UHL035A</t>
         </is>
       </c>
       <c r="E241" s="1" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="F241" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
@@ -8137,17 +8137,17 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>120041150002</t>
+          <t>101031250014</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>2%神經醯胺保濕精華15ML</t>
+          <t>玻尿酸保濕精華化妝水150ML</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t>DCS015A</t>
+          <t>HHT150A</t>
         </is>
       </c>
       <c r="E242" s="1" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="F242" s="1" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.23</t>
         </is>
       </c>
     </row>
@@ -8169,17 +8169,17 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>101051190015</t>
+          <t>101041150020</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華乳50ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>HHL050A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E243" s="1" t="inlineStr">
@@ -8189,29 +8189,29 @@
       </c>
       <c r="F243" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.27</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>29926125</t>
+          <t>29926127</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>104021280001</t>
+          <t>120041150002</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚潔膚露200ML</t>
+          <t>2%神經醯胺保濕精華15ML</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t>RRK200A</t>
+          <t>DCS015A</t>
         </is>
       </c>
       <c r="E244" s="1" t="inlineStr">
@@ -8221,29 +8221,29 @@
       </c>
       <c r="F244" s="1" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.26</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>29926125</t>
+          <t>29926127</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華 18% 15ML</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E245" s="1" t="inlineStr">
@@ -8265,17 +8265,17 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>104031250012</t>
+          <t>104021280001</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸毛孔緊緻化妝水150ML</t>
+          <t>杏仁酸溫和煥膚潔膚露200ML</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t>RRT150A</t>
+          <t>RRK200A</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="F246" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.21</t>
         </is>
       </c>
     </row>
@@ -8297,17 +8297,17 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>104241280002</t>
+          <t>104041150015</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚身體乳200ML</t>
+          <t>杏仁酸亮白煥膚精華 18% 15ML</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t>RBL200A</t>
+          <t>RRS015A</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
@@ -8317,71 +8317,71 @@
       </c>
       <c r="F247" s="1" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.24</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>29926128</t>
+          <t>29926125</t>
         </is>
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>104031250012</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>杏仁酸毛孔緊緻化妝水150ML</t>
         </is>
       </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>RRT150A</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F248" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>29926128</t>
+          <t>29926125</t>
         </is>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>104241280002</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>杏仁酸亮白煥膚身體乳200ML</t>
         </is>
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>RBL200A</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F249" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -8393,17 +8393,17 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
@@ -8420,64 +8420,64 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>29926129</t>
+          <t>29926128</t>
         </is>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E251" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F251" s="1" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>29926129</t>
+          <t>29926128</t>
         </is>
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D252" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E252" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F252" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
@@ -8489,49 +8489,49 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>122161050004</t>
+          <t>122161170001</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油5ML</t>
+          <t>角鯊潤澤修復精華油30ML</t>
         </is>
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t>QAS005A</t>
+          <t>QAS030A</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F253" s="1" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>29926130</t>
+          <t>29926129</t>
         </is>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>122161150001</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>角鯊潤澤修復精華油15ML</t>
         </is>
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>QAS015A</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
@@ -8541,39 +8541,39 @@
       </c>
       <c r="F254" s="1" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.35</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>29926130</t>
+          <t>29926129</t>
         </is>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>122161050004</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>角鯊潤澤修復精華油5ML</t>
         </is>
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>QAS005A</t>
         </is>
       </c>
       <c r="E255" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F255" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -8585,49 +8585,49 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>122161050003</t>
+          <t>122161170002</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油5ML</t>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
         </is>
       </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
-          <t>QRS005A</t>
+          <t>QRS030A</t>
         </is>
       </c>
       <c r="E256" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F256" s="1" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>29926131</t>
+          <t>29926130</t>
         </is>
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>104021250001</t>
+          <t>122161150004</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸煥膚潔顏慕斯150ML</t>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
         </is>
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
-          <t>RMK150A</t>
+          <t>QRS015A</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
@@ -8637,39 +8637,39 @@
       </c>
       <c r="F257" s="1" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.35</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>29926131</t>
+          <t>29926130</t>
         </is>
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>122161050003</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8% 15ML</t>
+          <t>角鯊玫瑰果賦活精華油5ML</t>
         </is>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t>RDS015A</t>
+          <t>QRS005A</t>
         </is>
       </c>
       <c r="E258" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F258" s="1" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -8681,25 +8681,89 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
+          <t>104021250001</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸煥膚潔顏慕斯150ML</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>RMK150A</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F259" s="1" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>29926131</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="inlineStr">
+        <is>
+          <t>104041150022</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸溫和煥膚精華8% 15ML</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>RDS015A</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F260" s="1" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>29926131</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="inlineStr">
+        <is>
           <t>115101040011</t>
         </is>
       </c>
-      <c r="C259" s="1" t="inlineStr">
+      <c r="C261" s="1" t="inlineStr">
         <is>
           <t>維他命A保濕修復膠囊面膜4入</t>
         </is>
       </c>
-      <c r="D259" s="1" t="inlineStr">
+      <c r="D261" s="1" t="inlineStr">
         <is>
           <t>VAM004A</t>
         </is>
       </c>
-      <c r="E259" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F259" s="1" t="inlineStr">
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>

--- a/mappings/組合對照表.xlsx
+++ b/mappings/組合對照表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F261"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1540,86 +1540,86 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>29925050</t>
+          <t>29925048</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>119041160003</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>超微C密集淡斑精華20ML</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>WSS020A</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>29925051</t>
+          <t>29925048</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>124031250001</t>
+          <t>120041150002</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華化妝水150ML</t>
+          <t>2%神經醯胺保濕精華15ML</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>WWT150A</t>
+          <t>DCS015A</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>29925058</t>
+          <t>29925048</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>101041170011</t>
+          <t>101031250014</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液30ML</t>
+          <t>玻尿酸保濕精華化妝水150ML</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>HHS030A</t>
+          <t>HHT150A</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1629,93 +1629,93 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.31</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>29925058</t>
+          <t>29925050</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>101041150017</t>
+          <t>119041160003</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>超微C密集淡斑精華20ML</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>WSS020A</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>29925059</t>
+          <t>29925051</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>104041170010</t>
+          <t>124031250001</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%30ML</t>
+          <t>超微C美白精華化妝水150ML</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>RRS030A</t>
+          <t>WWT150A</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>29925059</t>
+          <t>29925058</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%15ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -1725,29 +1725,29 @@
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.65</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>29925061</t>
+          <t>29925058</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>101041150017</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1757,29 +1757,29 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.35</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>29925061</t>
+          <t>29925059</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>104041170010</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>杏仁酸亮白煥膚精華18%30ML</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>RRS030A</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -1789,29 +1789,29 @@
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.65</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>29925062</t>
+          <t>29925059</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>104041150015</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>杏仁酸亮白煥膚精華18%15ML</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>RRS015A</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1821,29 +1821,29 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>29925062</t>
+          <t>29925061</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>122161170002</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>QRS030A</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -1853,61 +1853,61 @@
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.63</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>29925083</t>
+          <t>29925061</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>122161150004</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>QRS015A</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>29925091</t>
+          <t>29925062</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>101031250014</t>
+          <t>122161170001</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華化妝水150ML</t>
+          <t>角鯊潤澤修復精華油30ML</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>HHT150A</t>
+          <t>QAS030A</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1917,29 +1917,29 @@
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.62</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>29925091</t>
+          <t>29925062</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>101041170011</t>
+          <t>122161150001</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液30ML</t>
+          <t>角鯊潤澤修復精華油15ML</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>HHS030A</t>
+          <t>QAS015A</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -1949,61 +1949,61 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.38</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>29925092</t>
+          <t>29925083</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>101051190015</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華乳50ML</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>HHL050A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>29925092</t>
+          <t>29925091</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>101041170011</t>
+          <t>101031250014</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液30ML</t>
+          <t>玻尿酸保濕精華化妝水150ML</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>HHS030A</t>
+          <t>HHT150A</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2013,125 +2013,125 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>29925093</t>
+          <t>29925091</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>107111180010</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>全能保濕清爽防曬乳35ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>UHL035A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.67</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>29925094</t>
+          <t>29925092</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>107111180011</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>全能保濕潤色防曬乳35ML</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>UHT035A</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.35</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>29925095</t>
+          <t>29925092</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>107111180012</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>低敏物理舒緩防曬乳35ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>USL035A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.65</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>29925096</t>
+          <t>29925093</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>107111180013</t>
+          <t>107111180010</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>極效物理舒緩防曬乳35ML</t>
+          <t>全能保濕清爽防曬乳35ML</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>UXL035A</t>
+          <t>UHL035A</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2148,22 +2148,22 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>29925097</t>
+          <t>29925094</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>107111180014</t>
+          <t>107111180011</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>柔焦控油輕透防曬乳35ML</t>
+          <t>全能保濕潤色防曬乳35ML</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>UCL035A</t>
+          <t>UHT035A</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -2180,22 +2180,22 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>29925098</t>
+          <t>29925095</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>107111210001</t>
+          <t>107111180012</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>全日清爽身體防曬乳80ML</t>
+          <t>低敏物理舒緩防曬乳35ML</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>UBL080A</t>
+          <t>USL035A</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2212,118 +2212,118 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>29925107</t>
+          <t>29925096</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>101031250014</t>
+          <t>107111180013</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華化妝水150ML</t>
+          <t>極效物理舒緩防曬乳35ML</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>HHT150A</t>
+          <t>UXL035A</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>29925107</t>
+          <t>29925097</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>101051190015</t>
+          <t>107111180014</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華乳50ML</t>
+          <t>柔焦控油輕透防曬乳35ML</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>HHL050A</t>
+          <t>UCL035A</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>29925108</t>
+          <t>29925098</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>101041150017</t>
+          <t>107111210001</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>全日清爽身體防曬乳80ML</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>HHS015A(2408)</t>
+          <t>UBL080A</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>29925108</t>
+          <t>29925107</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>101101030013</t>
+          <t>101031250014</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕微導面膜3入</t>
+          <t>玻尿酸保濕精華化妝水150ML</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>HHM003A</t>
+          <t>HHT150A</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2333,29 +2333,29 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>29925109</t>
+          <t>29925107</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>104021280001</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚潔膚露200ML</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>RRK200A</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>29925109</t>
+          <t>29925108</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>101041150017</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8%15ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>RDS015A</t>
+          <t>HHS015A(2408)</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -2397,29 +2397,29 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.61</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>29925119</t>
+          <t>29925108</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>120041150019</t>
+          <t>101101030013</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>1%積雪草舒敏修護精華15ML</t>
+          <t>玻尿酸保濕微導面膜3入</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>DMS015A</t>
+          <t>HHM003A</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -2429,29 +2429,29 @@
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.39</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>29925119</t>
+          <t>29925109</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>115101040018</t>
+          <t>104021280001</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>積雪草舒敏精華面膜4入</t>
+          <t>杏仁酸溫和煥膚潔膚露200ML</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>DMM004A</t>
+          <t>RRK200A</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2461,29 +2461,29 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.47</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>29925120</t>
+          <t>29925109</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>120041150002</t>
+          <t>104041150022</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>2%神經醯胺保濕精華15ML</t>
+          <t>杏仁酸溫和煥膚精華8%15ML</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>DCS015A</t>
+          <t>RDS015A</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -2493,29 +2493,29 @@
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>29925120</t>
+          <t>29925111</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>115101040017</t>
+          <t>104041170010</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>神經醯胺保濕精華面膜4入</t>
+          <t>杏仁酸亮白煥膚精華18%30ML</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>DCM004A</t>
+          <t>RRS030A</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2525,29 +2525,29 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.49</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>29925121</t>
+          <t>29925111</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>104031250012</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>杏仁酸毛孔緊緻化妝水150ML</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>RRT150A</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -2557,29 +2557,29 @@
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>29925121</t>
+          <t>29925111</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>119041160003</t>
+          <t>104021250001</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>超微C密集淡斑精華20ML</t>
+          <t>杏仁酸煥膚潔顏慕斯150ML</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>WSS020A</t>
+          <t>RMK150A</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2589,29 +2589,29 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.23</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>29925123</t>
+          <t>29925119</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>120041150019</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>1%積雪草舒敏修護精華15ML</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>DMS015A</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -2621,29 +2621,29 @@
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>29925123</t>
+          <t>29925119</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>122161050001</t>
+          <t>115101040018</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油5ML</t>
+          <t>積雪草舒敏精華面膜4入</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>QAS005A</t>
+          <t>DMM004A</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2653,29 +2653,29 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>29925124</t>
+          <t>29925120</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>120041150002</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>2%神經醯胺保濕精華15ML</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>DCS015A</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
@@ -2685,29 +2685,29 @@
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.64</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>29925124</t>
+          <t>29925120</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>122161050002</t>
+          <t>115101040017</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油5ML</t>
+          <t>神經醯胺保濕精華面膜4入</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>QRS005A</t>
+          <t>DCM004A</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2717,29 +2717,29 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>29925145</t>
+          <t>29925121</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8%15ML</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>RDS015A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -2749,29 +2749,29 @@
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.58</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>29925145</t>
+          <t>29925121</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>119041160003</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%15ML</t>
+          <t>超微C密集淡斑精華20ML</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>WSS020A</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -2781,206 +2781,206 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.42</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>29925147</t>
+          <t>29925123</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>122161150001</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8%15ML</t>
+          <t>角鯊潤澤修復精華油15ML</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>RDS015A</t>
+          <t>QAS015A</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>29925148</t>
+          <t>29925123</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>102031250009</t>
+          <t>122161050001</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因前導精華露150ML</t>
+          <t>角鯊潤澤修復精華油5ML</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>AAT150A</t>
+          <t>QAS005A</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>29925149</t>
+          <t>29925124</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>102081150010</t>
+          <t>122161150004</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因撫紋眼霜15ML</t>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>AEC015A</t>
+          <t>QRS015A</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>29925150</t>
+          <t>29925124</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>115101040018</t>
+          <t>122161050002</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>積雪草舒敏精華面膜4入</t>
+          <t>角鯊玫瑰果賦活精華油5ML</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>DMM004A</t>
+          <t>QRS005A</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>29925151</t>
+          <t>29925145</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>115101040017</t>
+          <t>104041150022</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>神經醯胺保濕精華面膜4入</t>
+          <t>杏仁酸溫和煥膚精華8%15ML</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>DCM004A</t>
+          <t>RDS015A</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>29925152</t>
+          <t>29925145</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>115101040019</t>
+          <t>104041150015</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>白藜蘆醇亮白精華面膜4入</t>
+          <t>杏仁酸亮白煥膚精華18%15ML</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>DEM004A</t>
+          <t>RRS015A</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>29925175</t>
+          <t>29925147</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
@@ -3000,130 +3000,130 @@
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>29925175</t>
+          <t>29925148</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>104041050012</t>
+          <t>102031250009</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8% 5ML</t>
+          <t>超逆齡肌因前導精華露150ML</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>RDS005A</t>
+          <t>AAT150A</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>29925176</t>
+          <t>29925149</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>102081150010</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%15ML</t>
+          <t>超逆齡肌因撫紋眼霜15ML</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>AEC015A</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>29925176</t>
+          <t>29925150</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>104041050001</t>
+          <t>115101040018</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%5ML</t>
+          <t>積雪草舒敏精華面膜4入</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>RRS005A</t>
+          <t>DMM004A</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>29925178</t>
+          <t>29925151</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>104241280002</t>
+          <t>115101040017</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚身體乳200ML</t>
+          <t>神經醯胺保濕精華面膜4入</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>RBL200A</t>
+          <t>DCM004A</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -3140,219 +3140,219 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>29925180</t>
+          <t>29925152</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>115101040019</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>白藜蘆醇亮白精華面膜4入</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>DEM004A</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>29925180</t>
+          <t>29925164</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>119041150004</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液15ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>WWS015A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>29925182</t>
+          <t>29925175</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>104041150022</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽SHOT*7PCS</t>
+          <t>杏仁酸溫和煥膚精華8%15ML</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>RDS015A</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.71</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>29925183</t>
+          <t>29925175</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>104041050012</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
+          <t>杏仁酸溫和煥膚精華8% 5ML</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>RDS005A</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>29925184</t>
+          <t>29925176</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>104041150015</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽SHOT*7PCS</t>
+          <t>杏仁酸亮白煥膚精華18%15ML</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>RRS015A</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.71</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>29925185</t>
+          <t>29925176</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>104041050001</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽SHOT*7PCS</t>
+          <t>杏仁酸亮白煥膚精華18%5ML</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>RRS005A</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>29925186</t>
+          <t>29925178</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>104241280002</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
+          <t>杏仁酸亮白煥膚身體乳200ML</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>RBL200A</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
@@ -3364,182 +3364,182 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>29925187</t>
+          <t>29925180</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽SHOT*7PCS</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.62</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>29925188</t>
+          <t>29925180</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>101051190015</t>
+          <t>119041150004</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華乳50ML</t>
+          <t>超微C美白精華液15ML</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>HHL050A</t>
+          <t>WWS015A</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.38</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>29925188</t>
+          <t>29925182</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>115101040012</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>維他命B保濕舒緩膠囊面膜4入</t>
+          <t>水光雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>VBM004A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>29925189</t>
+          <t>29925183</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>101031250014</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華化妝水150ML</t>
+          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>HHT150A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>29925189</t>
+          <t>29925184</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>115101040012</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>維他命B保濕舒緩膠囊面膜4入</t>
+          <t>晚安雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>VBM004A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>29925190</t>
+          <t>29925185</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>101031250015</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華化妝水(清爽型)150ML</t>
+          <t>水光雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>HLT150A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3549,61 +3549,61 @@
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>29925190</t>
+          <t>29925186</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>115101040012</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>維他命B保濕舒緩膠囊面膜4入</t>
+          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>VBM004A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>29925191</t>
+          <t>29925187</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>101041170011</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液30ML</t>
+          <t>晚安雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>HHS030A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3613,445 +3613,445 @@
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>29925191</t>
+          <t>29925188</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>101041150017</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.89</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>29925192</t>
+          <t>29925188</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>104021250001</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸煥膚潔顏慕斯150ML</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>RMK150A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.11</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>29925192</t>
+          <t>29925189</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>115101040012</t>
+          <t>101031250014</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>維他命B保濕舒緩膠囊面膜4入</t>
+          <t>玻尿酸保濕精華化妝水150ML</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>VBM004A</t>
+          <t>HHT150A</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.89</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>29925193</t>
+          <t>29925189</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>104021280001</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚潔膚露200ML</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>RRK200A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.11</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>29925193</t>
+          <t>29925190</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>115101040011</t>
+          <t>101031250015</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>維他命A保濕修復膠囊面膜4入</t>
+          <t>玻尿酸保濕精華化妝水(清爽型)150ML</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>VAM004A</t>
+          <t>HLT150A</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.89</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>29925194</t>
+          <t>29925190</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>104031250012</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸毛孔緊緻化妝水150ML</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>RRT150A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.11</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>29925194</t>
+          <t>29925191</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>115101040011</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>維他命A保濕修復膠囊面膜4入</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>VAM004A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.87</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>29925195</t>
+          <t>29925191</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>104041170010</t>
+          <t>101041150017</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18% 30ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>RRS030A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>29925195</t>
+          <t>29925192</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>104021250001</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18% 15ML</t>
+          <t>杏仁酸煥膚潔顏慕斯150ML</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>RMK150A</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.88</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>29925196</t>
+          <t>29925192</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>29925196</t>
+          <t>29925193</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>104021280001</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>杏仁酸溫和煥膚潔膚露200ML</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>RRK200A</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.88</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>29925197</t>
+          <t>29925193</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>115101040011</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>維他命A保濕修復膠囊面膜4入</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>VAM004A</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>29925197</t>
+          <t>29925194</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>104031250012</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>杏仁酸毛孔緊緻化妝水150ML</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>RRT150A</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>29925208</t>
+          <t>29925194</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>102041170012</t>
+          <t>115101040011</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>維他命A保濕修復膠囊面膜4入</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>AAS030A(2507)</t>
+          <t>VAM004A</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4061,61 +4061,61 @@
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>29925208</t>
+          <t>29925195</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>102041150018</t>
+          <t>104041170010</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華15ML</t>
+          <t>杏仁酸亮白煥膚精華18% 30ML</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>AAS015A</t>
+          <t>RRS030A</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.88</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>29925209</t>
+          <t>29925195</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>102071170007</t>
+          <t>104041150015</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華霜30ML</t>
+          <t>杏仁酸亮白煥膚精華18% 15ML</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>AAC030A</t>
+          <t>RRS015A</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -4125,61 +4125,61 @@
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>29925209</t>
+          <t>29925196</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>102071150003</t>
+          <t>122161170001</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華霜15ML</t>
+          <t>角鯊潤澤修復精華油30ML</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>AAC015A</t>
+          <t>QAS030A</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.87</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>29925211</t>
+          <t>29925196</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>122161150001</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>角鯊潤澤修復精華油15ML</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>QAS015A</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -4189,61 +4189,61 @@
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>29925211</t>
+          <t>29925197</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>122161170002</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>QRS030A</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.87</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>29925212</t>
+          <t>29925197</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>101041170011</t>
+          <t>122161150004</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液30ML</t>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>HHS030A</t>
+          <t>QRS015A</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -4253,29 +4253,29 @@
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>29925212</t>
+          <t>29925208</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>101041150020</t>
+          <t>102041170012</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>AAS030A(2507)</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
@@ -4285,61 +4285,61 @@
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.63</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>29925213</t>
+          <t>29925208</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>123041150001</t>
+          <t>102041150018</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>超A醇煥顏緊緻精華1.5% 15ML</t>
+          <t>超逆齡肌因再生精華15ML</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>TLS015A</t>
+          <t>AAS015A</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>29925215</t>
+          <t>29925209</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>102071170007</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>超逆齡肌因再生精華霜30ML</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>AAC030A</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -4349,61 +4349,61 @@
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.68</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>29925215</t>
+          <t>29925209</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>102071150003</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>超逆齡肌因再生精華霜15ML</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>AAC015A</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.32</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>29925216</t>
+          <t>29925211</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>101031250014</t>
+          <t>122161170002</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華化妝水150ML</t>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>HHT150A</t>
+          <t>QRS030A</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -4413,46 +4413,46 @@
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.46</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>29925216</t>
+          <t>29925211</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>101051190015</t>
+          <t>122161150004</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華乳50ML</t>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>HHL050A</t>
+          <t>QRS015A</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.54</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>29925216</t>
+          <t>29925212</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.63</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>29925239</t>
+          <t>29925212</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
@@ -4509,61 +4509,61 @@
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>29925239</t>
+          <t>29925213</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>101101030013</t>
+          <t>123041150001</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕微導面膜3入</t>
+          <t>超A醇煥顏緊緻精華1.5% 15ML</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>HHM003A</t>
+          <t>TLS015A</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>29925240</t>
+          <t>29925215</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>122161170001</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>角鯊潤澤修復精華油30ML</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>QAS030A</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -4580,22 +4580,22 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>29925240</t>
+          <t>29925215</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>119041150004</t>
+          <t>122161150001</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液15ML</t>
+          <t>角鯊潤澤修復精華油15ML</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>WWS015A</t>
+          <t>QAS015A</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
@@ -4612,54 +4612,54 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>29925241</t>
+          <t>29925216</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>101031250014</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
+          <t>玻尿酸保濕精華化妝水150ML</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>HHT150A</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>29926008</t>
+          <t>29925216</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>101041170011</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液30ML</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>HHS030A</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -4669,61 +4669,61 @@
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.26</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>29926008</t>
+          <t>29925216</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>101041150020</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.49</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>29926009</t>
+          <t>29925225</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>115101040011</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>維他命A保濕修復膠囊面膜4入</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VAM004A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -4733,29 +4733,29 @@
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.09</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>29926009</t>
+          <t>29925225</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>115101040012</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>維他命B保濕舒緩膠囊面膜4入</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VBM004A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -4765,29 +4765,29 @@
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.38</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>29926009</t>
+          <t>29925225</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>115101040013</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>維他命C瞬效亮白膠囊面膜4入</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VCM004A</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -4797,29 +4797,29 @@
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>29926038</t>
+          <t>29925225</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>104041170010</t>
+          <t>101031250014</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%30ML</t>
+          <t>玻尿酸保濕精華化妝水150ML</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>RRS030A</t>
+          <t>HHT150A</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -4829,61 +4829,61 @@
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.18</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>29926038</t>
+          <t>29925225</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>101021250011</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%15ML</t>
+          <t>玻尿酸保濕潔顏慕斯150ML</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>HMK150A</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.16</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>29926039</t>
+          <t>29925226</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>104041170010</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%30ML</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>RRS030A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -4893,61 +4893,61 @@
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.09</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>29926039</t>
+          <t>29925226</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>104041150016</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%15ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>RRS015B</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.38</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>29926040</t>
+          <t>29925226</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>101051190015</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8%15ML</t>
+          <t>玻尿酸保濕精華乳50ML</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>RDS015A(2601)</t>
+          <t>HHL050A</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
@@ -4957,29 +4957,29 @@
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>29926040</t>
+          <t>29925226</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>104041150016</t>
+          <t>101031250015</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%15ML</t>
+          <t>玻尿酸保濕精華化妝水(清爽型)150ML</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>RRS015B</t>
+          <t>HLT150A</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -4989,29 +4989,29 @@
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.18</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>29926043</t>
+          <t>29925226</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>101021250011</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>玻尿酸保濕潔顏慕斯150ML</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>HMK150A</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -5021,61 +5021,61 @@
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.16</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>29926043</t>
+          <t>29925239</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>122161050001</t>
+          <t>101041150020</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油5ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>QAS005A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.61</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>29926044</t>
+          <t>29925239</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>101101030013</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>玻尿酸保濕微導面膜3入</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>HHM003A</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
@@ -5085,125 +5085,125 @@
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.39</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>29926044</t>
+          <t>29925240</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>122161050002</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油5ML</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>QRS005A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.45</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>29926045</t>
+          <t>29925240</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>119041150004</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>超微C美白精華液15ML</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>WWS015A</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.55</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>29926045</t>
+          <t>29925241</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>29926046</t>
+          <t>29926008</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>104041170010</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%30ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>RRS030A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -5213,61 +5213,61 @@
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>29926046</t>
+          <t>29926008</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>101041150020</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>29926047</t>
+          <t>29926009</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>123071170001</t>
+          <t>115101040011</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>超A醇煥顏緊緻精華霜 30ML</t>
+          <t>維他命A保濕修復膠囊面膜4入</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>TTC030A</t>
+          <t>VAM004A</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
@@ -5277,29 +5277,29 @@
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>29926047</t>
+          <t>29926009</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
@@ -5309,93 +5309,93 @@
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>29926048</t>
+          <t>29926009</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>102041170012</t>
+          <t>115101040013</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>維他命C瞬效亮白膠囊面膜4入</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>AAS030A(2507)</t>
+          <t>VCM004A</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>29926049</t>
+          <t>29926038</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>102071190005</t>
+          <t>104041170010</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華霜50ML</t>
+          <t>杏仁酸亮白煥膚精華18%30ML</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>AAC050A</t>
+          <t>RRS030A</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.48</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>29926050</t>
+          <t>29926038</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>113051360001</t>
+          <t>104041150015</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>瞬適膚舒緩修護保濕乳250ML</t>
+          <t>杏仁酸亮白煥膚精華18%15ML</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>SBL250A</t>
+          <t>RRS015A</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
@@ -5405,61 +5405,61 @@
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.52</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>29926051</t>
+          <t>29926039</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>125091410001</t>
+          <t>104041170010</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>瞬適膚舒緩潤澤修護霜280ML</t>
+          <t>杏仁酸亮白煥膚精華18%30ML</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>SBC280A</t>
+          <t>RRS030A</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.48</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>29926052</t>
+          <t>29926039</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>125091190001</t>
+          <t>104041150016</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>瞬適膚舒緩保濕護手霜 50ML</t>
+          <t>杏仁酸亮白煥膚精華18%15ML</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>SHC050A</t>
+          <t>RRS015B</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
@@ -5469,29 +5469,29 @@
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.52</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>29926057</t>
+          <t>29926040</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>102041170013</t>
+          <t>104041150022</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>杏仁酸溫和煥膚精華8%15ML</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>AAS030A</t>
+          <t>RDS015A(2601)</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
@@ -5501,29 +5501,29 @@
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>29926057</t>
+          <t>29926040</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>102071190005</t>
+          <t>104041150016</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華霜50ML</t>
+          <t>杏仁酸亮白煥膚精華18%15ML</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>AAC050A</t>
+          <t>RRS015B</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
@@ -5533,29 +5533,29 @@
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>29926058</t>
+          <t>29926043</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>102031250009</t>
+          <t>122161170001</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因前導精華露150ML</t>
+          <t>角鯊潤澤修復精華油30ML</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>AAT150A</t>
+          <t>QAS030A</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -5565,34 +5565,34 @@
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.63</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>29926058</t>
+          <t>29926043</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>102041170013</t>
+          <t>122161050001</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>角鯊潤澤修復精華油5ML</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>AAS030A</t>
+          <t>QAS005A</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
@@ -5604,22 +5604,22 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>29926058</t>
+          <t>29926044</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>102071190005</t>
+          <t>122161170002</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華霜50ML</t>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>AAC050A</t>
+          <t>QRS030A</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
@@ -5629,61 +5629,61 @@
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.63</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>29926059</t>
+          <t>29926044</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>102031250009</t>
+          <t>122161050002</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因前導精華露150ML</t>
+          <t>角鯊玫瑰果賦活精華油5ML</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>AAT150A</t>
+          <t>QRS005A</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>29926059</t>
+          <t>29926045</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>102041170013</t>
+          <t>122161170001</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>角鯊潤澤修復精華油30ML</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>AAS030A</t>
+          <t>QAS030A</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
@@ -5693,29 +5693,29 @@
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.48</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>29926059</t>
+          <t>29926045</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>102071190005</t>
+          <t>122161170002</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華霜50ML</t>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>AAC050A</t>
+          <t>QRS030A</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.52</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>29926059</t>
+          <t>29926046</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>102081150010</t>
+          <t>104041170010</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因撫紋眼霜15ML</t>
+          <t>杏仁酸亮白煥膚精華18%30ML</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>AEC015A</t>
+          <t>RRS030A</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -5757,29 +5757,29 @@
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.47</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>29926060</t>
+          <t>29926046</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
@@ -5789,29 +5789,29 @@
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.53</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>29926060</t>
+          <t>29926047</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>121041190002</t>
+          <t>123071170001</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超時空抗皺修復霜50ML</t>
+          <t>超A醇煥顏緊緻精華霜 30ML</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>XSC050A</t>
+          <t>TTC030A</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
@@ -5821,29 +5821,29 @@
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.47</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>29926061</t>
+          <t>29926047</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
@@ -5853,174 +5853,174 @@
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.53</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>29926061</t>
+          <t>29926048</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>121041190002</t>
+          <t>102041170012</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超時空抗皺修復霜50ML</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t>XSC050A</t>
+          <t>AAS030A(2507)</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F171" s="1" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>29926062</t>
+          <t>29926049</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>102031250009</t>
+          <t>102071190005</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因前導精華露150ML</t>
+          <t>超逆齡肌因再生精華霜50ML</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
         <is>
-          <t>AAT150A</t>
+          <t>AAC050A</t>
         </is>
       </c>
       <c r="E172" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F172" s="1" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>29926062</t>
+          <t>29926050</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>121041310003</t>
+          <t>113051360001</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超級全能精華40ML</t>
+          <t>瞬適膚舒緩修護保濕乳250ML</t>
         </is>
       </c>
       <c r="D173" s="1" t="inlineStr">
         <is>
-          <t>XSS040A</t>
+          <t>SBL250A</t>
         </is>
       </c>
       <c r="E173" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F173" s="1" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>29926063</t>
+          <t>29926051</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>102071190005</t>
+          <t>125091410001</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華霜50ML</t>
+          <t>瞬適膚舒緩潤澤修護霜280ML</t>
         </is>
       </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>AAC050A</t>
+          <t>SBC280A</t>
         </is>
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>29926063</t>
+          <t>29926052</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>121041310003</t>
+          <t>125091190001</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超級全能精華40ML</t>
+          <t>瞬適膚舒緩保濕護手霜 50ML</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t>XSS040A</t>
+          <t>SHC050A</t>
         </is>
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>29926064</t>
+          <t>29926057</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
@@ -6045,29 +6045,29 @@
       </c>
       <c r="F176" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.46</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>29926064</t>
+          <t>29926057</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>121031250001</t>
+          <t>102071190005</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超微導肌活精華露150ML</t>
+          <t>超逆齡肌因再生精華霜50ML</t>
         </is>
       </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t>XST150A</t>
+          <t>AAC050A</t>
         </is>
       </c>
       <c r="E177" s="1" t="inlineStr">
@@ -6077,29 +6077,29 @@
       </c>
       <c r="F177" s="1" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.54</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>29926065</t>
+          <t>29926058</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>102031250009</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華18%15ML</t>
+          <t>超逆齡肌因前導精華露150ML</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>AAT150A</t>
         </is>
       </c>
       <c r="E178" s="1" t="inlineStr">
@@ -6109,29 +6109,29 @@
       </c>
       <c r="F178" s="1" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>29926065</t>
+          <t>29926058</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>104241280002</t>
+          <t>102041170013</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚身體乳200ML</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>RBL200A</t>
+          <t>AAS030A</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
@@ -6141,29 +6141,29 @@
       </c>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>29926078</t>
+          <t>29926058</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>121041310003</t>
+          <t>102071190005</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超級全能精華40ML</t>
+          <t>超逆齡肌因再生精華霜50ML</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>XSS040A</t>
+          <t>AAC050A</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -6173,29 +6173,29 @@
       </c>
       <c r="F180" s="1" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>29926078</t>
+          <t>29926059</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>121041190002</t>
+          <t>102031250009</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超時空抗皺修復霜50ML</t>
+          <t>超逆齡肌因前導精華露150ML</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>XSC050A</t>
+          <t>AAT150A</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -6205,29 +6205,29 @@
       </c>
       <c r="F181" s="1" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.16</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>29926078</t>
+          <t>29926059</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>121021400001</t>
+          <t>102041170013</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚活性平衡潔顏乳125G</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>XSK125A</t>
+          <t>AAS030A</t>
         </is>
       </c>
       <c r="E182" s="1" t="inlineStr">
@@ -6237,29 +6237,29 @@
       </c>
       <c r="F182" s="1" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>29926079</t>
+          <t>29926059</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>121031250001</t>
+          <t>102071190005</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超微導肌活精華露150ML</t>
+          <t>超逆齡肌因再生精華霜50ML</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
         <is>
-          <t>XST150A</t>
+          <t>AAC050A</t>
         </is>
       </c>
       <c r="E183" s="1" t="inlineStr">
@@ -6269,29 +6269,29 @@
       </c>
       <c r="F183" s="1" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>29926079</t>
+          <t>29926059</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>121041310003</t>
+          <t>102081150010</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超級全能精華40ML</t>
+          <t>超逆齡肌因撫紋眼霜15ML</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t>XSS040A</t>
+          <t>AEC015A</t>
         </is>
       </c>
       <c r="E184" s="1" t="inlineStr">
@@ -6301,29 +6301,29 @@
       </c>
       <c r="F184" s="1" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.21</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>29926079</t>
+          <t>29926060</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>121041190002</t>
+          <t>122161170001</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超時空抗皺修復霜50ML</t>
+          <t>角鯊潤澤修復精華油30ML</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t>XSC050A</t>
+          <t>QAS030A</t>
         </is>
       </c>
       <c r="E185" s="1" t="inlineStr">
@@ -6333,29 +6333,29 @@
       </c>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>29926079</t>
+          <t>29926060</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>121081150001</t>
+          <t>121041190002</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚超能無痕抗皺眼霜15ML</t>
+          <t>瑞德膚超時空抗皺修復霜50ML</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t>XEC015A</t>
+          <t>XSC050A</t>
         </is>
       </c>
       <c r="E186" s="1" t="inlineStr">
@@ -6365,29 +6365,29 @@
       </c>
       <c r="F186" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.69</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>29926079</t>
+          <t>29926061</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>121011280001</t>
+          <t>122161170002</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚回歸純淨卸妝菁萃200ML</t>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
         </is>
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>XSR200A</t>
+          <t>QRS030A</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
@@ -6397,29 +6397,29 @@
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>29926079</t>
+          <t>29926061</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>121021400001</t>
+          <t>121041190002</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>瑞德膚活性平衡潔顏乳125G</t>
+          <t>瑞德膚超時空抗皺修復霜50ML</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>XSK125A</t>
+          <t>XSC050A</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
@@ -6429,61 +6429,61 @@
       </c>
       <c r="F188" s="1" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.67</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>29926082</t>
+          <t>29926062</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>102041170013</t>
+          <t>102031250009</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>超逆齡肌因前導精華露150ML</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t>AAS030A</t>
+          <t>AAT150A</t>
         </is>
       </c>
       <c r="E189" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.21</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>29926083</t>
+          <t>29926062</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>124031250001</t>
+          <t>121041310003</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華化妝水150ML</t>
+          <t>瑞德膚超級全能精華40ML</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>WWT150A</t>
+          <t>XSS040A</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -6493,29 +6493,29 @@
       </c>
       <c r="F190" s="1" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.79</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>29926083</t>
+          <t>29926063</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>102071190005</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>超逆齡肌因再生精華霜50ML</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>AAC050A</t>
         </is>
       </c>
       <c r="E191" s="1" t="inlineStr">
@@ -6525,29 +6525,29 @@
       </c>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>29926083</t>
+          <t>29926063</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>119041160003</t>
+          <t>121041310003</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>超微C密集淡斑精華20ML</t>
+          <t>瑞德膚超級全能精華40ML</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t>WSS020A</t>
+          <t>XSS040A</t>
         </is>
       </c>
       <c r="E192" s="1" t="inlineStr">
@@ -6557,61 +6557,61 @@
       </c>
       <c r="F192" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.63</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>29926085</t>
+          <t>29926064</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>101041170011</t>
+          <t>102041170013</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液30ML</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>HHS030A</t>
+          <t>AAS030A</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.55</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>29926085</t>
+          <t>29926064</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>101041150020</t>
+          <t>121031250001</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>瑞德膚超微導肌活精華露150ML</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>XST150A</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -6621,29 +6621,29 @@
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.45</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>29926095</t>
+          <t>29926065</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>101041150020</t>
+          <t>104041150015</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>杏仁酸亮白煥膚精華18%15ML</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>RRS015A</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
@@ -6653,29 +6653,29 @@
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>29926095</t>
+          <t>29926065</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>101041050007</t>
+          <t>104241280002</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液5ML</t>
+          <t>杏仁酸亮白煥膚身體乳200ML</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t>HHS005A</t>
+          <t>RBL200A</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
@@ -6685,221 +6685,221 @@
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.56</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>29926096</t>
+          <t>29926078</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>107111430001</t>
+          <t>121041310003</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>輕透水感物理防曬液38ML</t>
+          <t>瑞德膚超級全能精華40ML</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>UMF038A</t>
+          <t>XSS040A</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F197" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>29926100</t>
+          <t>29926078</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>20123029</t>
+          <t>121041190002</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕微導面膜8入組</t>
+          <t>瑞德膚超時空抗皺修復霜50ML</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>PB230701=HHM001X*8</t>
+          <t>XSC050A</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>29926101</t>
+          <t>29926078</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>115101040018</t>
+          <t>121021400001</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>積雪草舒敏精華面膜4入</t>
+          <t>瑞德膚活性平衡潔顏乳125G</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>DMM004A</t>
+          <t>XSK125A</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>29926101</t>
+          <t>29926079</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>115101040017</t>
+          <t>121031250001</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>神經醯胺保濕精華面膜4入</t>
+          <t>瑞德膚超微導肌活精華露150ML</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>DCM004A</t>
+          <t>XST150A</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.11</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>29926101</t>
+          <t>29926079</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>115101040019</t>
+          <t>121041310003</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>白藜蘆醇亮白精華面膜4入</t>
+          <t>瑞德膚超級全能精華40ML</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>DEM004A</t>
+          <t>XSS040A</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>29926102</t>
+          <t>29926079</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>121041190002</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽SHOT*7PCS</t>
+          <t>瑞德膚超時空抗皺修復霜50ML</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>XSC050A</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F202" s="1" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.28</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>29926102</t>
+          <t>29926079</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>121081150001</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
+          <t>瑞德膚超能無痕抗皺眼霜15ML</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>XEC015A</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
@@ -6909,61 +6909,61 @@
       </c>
       <c r="F203" s="1" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>29926103</t>
+          <t>29926079</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>121011280001</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽SHOT*7PCS</t>
+          <t>瑞德膚回歸純淨卸妝菁萃200ML</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>XSR200A</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F204" s="1" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.09</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>29926103</t>
+          <t>29926079</t>
         </is>
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>121021400001</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
+          <t>瑞德膚活性平衡潔顏乳125G</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>XSK125A</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
@@ -6973,61 +6973,61 @@
       </c>
       <c r="F205" s="1" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>29926104</t>
+          <t>29926082</t>
         </is>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>102041170013</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>AAS030A</t>
         </is>
       </c>
       <c r="E206" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F206" s="1" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>29926104</t>
+          <t>29926083</t>
         </is>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>124031250001</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
+          <t>超微C美白精華化妝水150ML</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>WWT150A</t>
         </is>
       </c>
       <c r="E207" s="1" t="inlineStr">
@@ -7037,29 +7037,29 @@
       </c>
       <c r="F207" s="1" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.23</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>29926105</t>
+          <t>29926083</t>
         </is>
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽SHOT*7PCS</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -7069,29 +7069,29 @@
       </c>
       <c r="F208" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>29926105</t>
+          <t>29926083</t>
         </is>
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>119041160003</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
+          <t>超微C密集淡斑精華20ML</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>WSS020A</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
@@ -7108,22 +7108,22 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>29926105</t>
+          <t>29926084</t>
         </is>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>115101040012</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽SHOT*7PCS</t>
+          <t>維他命B保濕舒緩膠囊面膜4入</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>VBM004A</t>
         </is>
       </c>
       <c r="E210" s="1" t="inlineStr">
@@ -7133,93 +7133,93 @@
       </c>
       <c r="F210" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>29926107</t>
+          <t>29926084</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>101021250011</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>玻尿酸保濕潔顏慕斯150ML</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>HMK150A</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F211" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.88</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>29926107</t>
+          <t>29926085</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>122161050004</t>
+          <t>101041170011</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油5ML</t>
+          <t>玻尿酸保濕精華液30ML</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>QAS005A</t>
+          <t>HHS030A</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F212" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.87</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>29926108</t>
+          <t>29926085</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>101041150020</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
@@ -7229,29 +7229,29 @@
       </c>
       <c r="F213" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>29926108</t>
+          <t>29926095</t>
         </is>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>122161050003</t>
+          <t>101041150020</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油5ML</t>
+          <t>玻尿酸保濕精華液15ML</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t>QRS005A</t>
+          <t>HHS015A</t>
         </is>
       </c>
       <c r="E214" s="1" t="inlineStr">
@@ -7261,61 +7261,61 @@
       </c>
       <c r="F214" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>29926106</t>
+          <t>29926095</t>
         </is>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>102041170013</t>
+          <t>101041050007</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>超逆齡肌因再生精華30ML</t>
+          <t>玻尿酸保濕精華液5ML</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>AAS030A</t>
+          <t>HHS005A</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F215" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>29926110</t>
+          <t>29926096</t>
         </is>
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>107111430001</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>輕透水感物理防曬液38ML</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>UMF038A</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
@@ -7325,61 +7325,61 @@
       </c>
       <c r="F216" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>29926110</t>
+          <t>29926100</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>151171070004</t>
+          <t>20123029</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
+          <t>玻尿酸保濕微導面膜8入組</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t>SCP007A</t>
+          <t>PB230701=HHM001X*8</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F217" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>29926111</t>
+          <t>29926101</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>115101040018</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>積雪草舒敏精華面膜4入</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>DMM004A</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -7389,61 +7389,61 @@
       </c>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>29926111</t>
+          <t>29926101</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>151171070004</t>
+          <t>115101040017</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
+          <t>神經醯胺保濕精華面膜4入</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>SCP007A</t>
+          <t>DCM004A</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F219" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>29926112</t>
+          <t>29926101</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>115101040019</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>白藜蘆醇亮白精華面膜4入</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>DEM004A</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
@@ -7453,61 +7453,61 @@
       </c>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>29926112</t>
+          <t>29926102</t>
         </is>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>151171070004</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
+          <t>晚安雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>SCP007A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>29926113</t>
+          <t>29926102</t>
         </is>
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
@@ -7517,61 +7517,61 @@
       </c>
       <c r="F222" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>29926113</t>
+          <t>29926103</t>
         </is>
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F223" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>29926113</t>
+          <t>29926103</t>
         </is>
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
         </is>
       </c>
       <c r="D224" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
@@ -7581,93 +7581,93 @@
       </c>
       <c r="F224" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>29926113</t>
+          <t>29926104</t>
         </is>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>151171070004</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
+          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>SCP007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F225" s="1" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>29926114</t>
+          <t>29926104</t>
         </is>
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>雙膠原蛋白胜肽粉4.5G*28PCS</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F226" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>29926114</t>
+          <t>29926105</t>
         </is>
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
+          <t>水光雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="F227" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>29926115</t>
+          <t>29926105</t>
         </is>
       </c>
       <c r="B228" s="1" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>亮妍雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
@@ -7704,34 +7704,34 @@
       </c>
       <c r="E228" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F228" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>29926115</t>
+          <t>29926105</t>
         </is>
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
+          <t>晚安雙膠原胜肽SHOT*7PCS</t>
         </is>
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
@@ -7741,61 +7741,61 @@
       </c>
       <c r="F229" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>29926116</t>
+          <t>29926107</t>
         </is>
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>122161150001</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>角鯊潤澤修復精華油15ML</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>QAS015A</t>
         </is>
       </c>
       <c r="E230" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F230" s="1" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>29926116</t>
+          <t>29926107</t>
         </is>
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>151171070002</t>
+          <t>122161050004</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
+          <t>角鯊潤澤修復精華油5ML</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t>SCP028A</t>
+          <t>QAS005A</t>
         </is>
       </c>
       <c r="E231" s="1" t="inlineStr">
@@ -7805,125 +7805,125 @@
       </c>
       <c r="F231" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>29926117</t>
+          <t>29926108</t>
         </is>
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>122161150004</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
         </is>
       </c>
       <c r="D232" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>QRS015A</t>
         </is>
       </c>
       <c r="E232" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F232" s="1" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>29926117</t>
+          <t>29926108</t>
         </is>
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>122161050003</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>角鯊玫瑰果賦活精華油5ML</t>
         </is>
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>QRS005A</t>
         </is>
       </c>
       <c r="E233" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F233" s="1" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.25</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>29926118</t>
+          <t>29926106</t>
         </is>
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>102041170013</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>超逆齡肌因再生精華30ML</t>
         </is>
       </c>
       <c r="D234" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>AAS030A</t>
         </is>
       </c>
       <c r="E234" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F234" s="1" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>29926118</t>
+          <t>29926110</t>
         </is>
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E235" s="1" t="inlineStr">
@@ -7933,61 +7933,61 @@
       </c>
       <c r="F235" s="1" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>29926119</t>
+          <t>29926110</t>
         </is>
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151171070004</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
         </is>
       </c>
       <c r="D236" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SCP007A</t>
         </is>
       </c>
       <c r="E236" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F236" s="1" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>29926119</t>
+          <t>29926111</t>
         </is>
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E237" s="1" t="inlineStr">
@@ -7997,29 +7997,29 @@
       </c>
       <c r="F237" s="1" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>29926124</t>
+          <t>29926111</t>
         </is>
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>151171070004</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8% 15ML</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t>RDS015A</t>
+          <t>SCP007A</t>
         </is>
       </c>
       <c r="E238" s="1" t="inlineStr">
@@ -8029,61 +8029,61 @@
       </c>
       <c r="F238" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>29926124</t>
+          <t>29926112</t>
         </is>
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>104041160001</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸淨痘調理精華20ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>RSS020A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E239" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F239" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>29926126</t>
+          <t>29926112</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>119041170003</t>
+          <t>151171070004</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>超微C美白精華液30ML</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t>WWS030A</t>
+          <t>SCP007A</t>
         </is>
       </c>
       <c r="E240" s="1" t="inlineStr">
@@ -8093,29 +8093,29 @@
       </c>
       <c r="F240" s="1" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>29926126</t>
+          <t>29926113</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>107111180010</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>全能保濕清爽防曬乳35ML</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t>UHL035A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E241" s="1" t="inlineStr">
@@ -8125,29 +8125,29 @@
       </c>
       <c r="F241" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.27</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>29926127</t>
+          <t>29926113</t>
         </is>
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>101031250014</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華化妝水150ML</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t>HHT150A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E242" s="1" t="inlineStr">
@@ -8157,29 +8157,29 @@
       </c>
       <c r="F242" s="1" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.27</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>29926127</t>
+          <t>29926113</t>
         </is>
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>101041150020</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華液15ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>HHS015A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E243" s="1" t="inlineStr">
@@ -8196,86 +8196,86 @@
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>29926127</t>
+          <t>29926113</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>120041150002</t>
+          <t>151171070004</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t>2%神經醯胺保濕精華15ML</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 7入</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t>DCS015A</t>
+          <t>SCP007A</t>
         </is>
       </c>
       <c r="E244" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F244" s="1" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.18</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>29926127</t>
+          <t>29926114</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>101051190015</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸保濕精華乳50ML</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t>HHL050A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E245" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F245" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>29926125</t>
+          <t>29926114</t>
         </is>
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>104021280001</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚潔膚露200ML</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t>RRK200A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
@@ -8285,61 +8285,61 @@
       </c>
       <c r="F246" s="1" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>29926125</t>
+          <t>29926115</t>
         </is>
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>104041150015</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚精華 18% 15ML</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t>RRS015A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F247" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>29926125</t>
+          <t>29926115</t>
         </is>
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>104031250012</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸毛孔緊緻化妝水150ML</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
         </is>
       </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
-          <t>RRT150A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
@@ -8349,189 +8349,189 @@
       </c>
       <c r="F248" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>29926125</t>
+          <t>29926116</t>
         </is>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>104241280002</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸亮白煥膚身體乳200ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t>RBL200A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F249" s="1" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.86</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>29926128</t>
+          <t>29926116</t>
         </is>
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>151131070002</t>
+          <t>151171070002</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
         <is>
-          <t>水光雙膠原胜肽飲7入</t>
+          <t>雙膠原蛋白胜肽粉4.5G X 28入</t>
         </is>
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t>SHS007A</t>
+          <t>SCP028A</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F250" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>29926128</t>
+          <t>29926117</t>
         </is>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>151131070001</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t>亮妍雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t>SBS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E251" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F251" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.83</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>29926128</t>
+          <t>29926117</t>
         </is>
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>151131070003</t>
+          <t>151131070002</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t>晚安雙膠原胜肽飲7入</t>
+          <t>水光雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D252" s="1" t="inlineStr">
         <is>
-          <t>SNS007A</t>
+          <t>SHS007A</t>
         </is>
       </c>
       <c r="E252" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F252" s="1" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>29926129</t>
+          <t>29926118</t>
         </is>
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>122161170001</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油30ML</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t>QAS030A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F253" s="1" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.83</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>29926129</t>
+          <t>29926118</t>
         </is>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>122161150001</t>
+          <t>151131070001</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油15ML</t>
+          <t>亮妍雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t>QAS015A</t>
+          <t>SBS007A</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
@@ -8541,61 +8541,61 @@
       </c>
       <c r="F254" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.17</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>29926129</t>
+          <t>29926119</t>
         </is>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>122161050004</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t>角鯊潤澤修復精華油5ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t>QAS005A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E255" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F255" s="1" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.83</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>29926130</t>
+          <t>29926119</t>
         </is>
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>122161170002</t>
+          <t>151131070003</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油30ML</t>
+          <t>晚安雙膠原胜肽飲7入</t>
         </is>
       </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
-          <t>QRS030A</t>
+          <t>SNS007A</t>
         </is>
       </c>
       <c r="E256" s="1" t="inlineStr">
@@ -8605,61 +8605,61 @@
       </c>
       <c r="F256" s="1" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.17</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>29926130</t>
+          <t>29926124</t>
         </is>
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>122161150004</t>
+          <t>104041150022</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油15ML</t>
+          <t>杏仁酸溫和煥膚精華8% 15ML</t>
         </is>
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
-          <t>QRS015A</t>
+          <t>RDS015A</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F257" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.52</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>29926130</t>
+          <t>29926124</t>
         </is>
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>122161050003</t>
+          <t>104041160001</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t>角鯊玫瑰果賦活精華油5ML</t>
+          <t>杏仁酸淨痘調理精華20ML</t>
         </is>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t>QRS005A</t>
+          <t>RSS020A</t>
         </is>
       </c>
       <c r="E258" s="1" t="inlineStr">
@@ -8669,101 +8669,709 @@
       </c>
       <c r="F258" s="1" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.48</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>29926131</t>
+          <t>29926126</t>
         </is>
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>104021250001</t>
+          <t>119041170003</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸煥膚潔顏慕斯150ML</t>
+          <t>超微C美白精華液30ML</t>
         </is>
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t>RMK150A</t>
+          <t>WWS030A</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F259" s="1" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.67</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>29926131</t>
+          <t>29926126</t>
         </is>
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>104041150022</t>
+          <t>107111180010</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
-          <t>杏仁酸溫和煥膚精華8% 15ML</t>
+          <t>全能保濕清爽防曬乳35ML</t>
         </is>
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>RDS015A</t>
+          <t>UHL035A</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F260" s="1" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
+          <t>29926127</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="inlineStr">
+        <is>
+          <t>101031250014</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>玻尿酸保濕精華化妝水150ML</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>HHT150A</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>29926127</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="inlineStr">
+        <is>
+          <t>101041150020</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>玻尿酸保濕精華液15ML</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>HHS015A</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F262" s="1" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>29926127</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="inlineStr">
+        <is>
+          <t>120041150002</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>2%神經醯胺保濕精華15ML</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>DCS015A</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F263" s="1" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>29926127</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="inlineStr">
+        <is>
+          <t>101051190015</t>
+        </is>
+      </c>
+      <c r="C264" s="1" t="inlineStr">
+        <is>
+          <t>玻尿酸保濕精華乳50ML</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t>HHL050A</t>
+        </is>
+      </c>
+      <c r="E264" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F264" s="1" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>29926125</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t>104021280001</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸溫和煥膚潔膚露200ML</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>RRK200A</t>
+        </is>
+      </c>
+      <c r="E265" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F265" s="1" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>29926125</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="inlineStr">
+        <is>
+          <t>104041150015</t>
+        </is>
+      </c>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸亮白煥膚精華 18% 15ML</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="inlineStr">
+        <is>
+          <t>RRS015A</t>
+        </is>
+      </c>
+      <c r="E266" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F266" s="1" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>29926125</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t>104031250012</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸毛孔緊緻化妝水150ML</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t>RRT150A</t>
+        </is>
+      </c>
+      <c r="E267" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F267" s="1" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>29926125</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="inlineStr">
+        <is>
+          <t>104241280002</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸亮白煥膚身體乳200ML</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="inlineStr">
+        <is>
+          <t>RBL200A</t>
+        </is>
+      </c>
+      <c r="E268" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F268" s="1" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>29926128</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="inlineStr">
+        <is>
+          <t>151131070002</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>水光雙膠原胜肽飲7入</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="inlineStr">
+        <is>
+          <t>SHS007A</t>
+        </is>
+      </c>
+      <c r="E269" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F269" s="1" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>29926128</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="inlineStr">
+        <is>
+          <t>151131070001</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>亮妍雙膠原胜肽飲7入</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t>SBS007A</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F270" s="1" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>29926128</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="inlineStr">
+        <is>
+          <t>151131070003</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>晚安雙膠原胜肽飲7入</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr">
+        <is>
+          <t>SNS007A</t>
+        </is>
+      </c>
+      <c r="E271" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F271" s="1" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>29926129</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="inlineStr">
+        <is>
+          <t>122161170001</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>角鯊潤澤修復精華油30ML</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="inlineStr">
+        <is>
+          <t>QAS030A</t>
+        </is>
+      </c>
+      <c r="E272" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F272" s="1" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>29926129</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="inlineStr">
+        <is>
+          <t>122161150001</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>角鯊潤澤修復精華油15ML</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr">
+        <is>
+          <t>QAS015A</t>
+        </is>
+      </c>
+      <c r="E273" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F273" s="1" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>29926129</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t>122161050004</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>角鯊潤澤修復精華油5ML</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t>QAS005A</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F274" s="1" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>29926130</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="inlineStr">
+        <is>
+          <t>122161170002</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>角鯊玫瑰果賦活精華油30ML</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="inlineStr">
+        <is>
+          <t>QRS030A</t>
+        </is>
+      </c>
+      <c r="E275" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F275" s="1" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>29926130</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="inlineStr">
+        <is>
+          <t>122161150004</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>角鯊玫瑰果賦活精華油15ML</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="inlineStr">
+        <is>
+          <t>QRS015A</t>
+        </is>
+      </c>
+      <c r="E276" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F276" s="1" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>29926130</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="inlineStr">
+        <is>
+          <t>122161050003</t>
+        </is>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>角鯊玫瑰果賦活精華油5ML</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="inlineStr">
+        <is>
+          <t>QRS005A</t>
+        </is>
+      </c>
+      <c r="E277" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F277" s="1" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
           <t>29926131</t>
         </is>
       </c>
-      <c r="B261" s="1" t="inlineStr">
+      <c r="B278" s="1" t="inlineStr">
+        <is>
+          <t>104021250001</t>
+        </is>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸煥膚潔顏慕斯150ML</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="inlineStr">
+        <is>
+          <t>RMK150A</t>
+        </is>
+      </c>
+      <c r="E278" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F278" s="1" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>29926131</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="inlineStr">
+        <is>
+          <t>104041150022</t>
+        </is>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>杏仁酸溫和煥膚精華8% 15ML</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t>RDS015A</t>
+        </is>
+      </c>
+      <c r="E279" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F279" s="1" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>29926131</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="inlineStr">
         <is>
           <t>115101040011</t>
         </is>
       </c>
-      <c r="C261" s="1" t="inlineStr">
+      <c r="C280" s="1" t="inlineStr">
         <is>
           <t>維他命A保濕修復膠囊面膜4入</t>
         </is>
       </c>
-      <c r="D261" s="1" t="inlineStr">
+      <c r="D280" s="1" t="inlineStr">
         <is>
           <t>VAM004A</t>
         </is>
       </c>
-      <c r="E261" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F261" s="1" t="inlineStr">
+      <c r="E280" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F280" s="1" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
